--- a/artfynd/A 27135-2026 artfynd.xlsx
+++ b/artfynd/A 27135-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2756399</v>
+        <v>80064</v>
       </c>
       <c r="B2" t="n">
-        <v>107007</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220320</v>
+        <v>174</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ängsskära</t>
+          <t>Strävlosta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Serratula tinctoria</t>
+          <t>Bromopsis benekenii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lange) Holub</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>frukt-/fröspridning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>671769.7158411201</v>
+        <v>671770</v>
       </c>
       <c r="R2" t="n">
-        <v>6546836.174083618</v>
+        <v>6546836</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,24 +748,14 @@
           <t>2006-09-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-09-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>t.a., i omr.</t>
+          <t>T.a.; Känd tidigare...</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>ädellövskog, ängsmark</t>
+          <t>Ädellövskog, mot berg; Rik lövmylla</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,43 +787,47 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>80064</v>
+        <v>263504</v>
       </c>
       <c r="B3" t="n">
-        <v>97511</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>174</v>
+        <v>783</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strävlosta</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bromopsis benekenii</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lange) Holub</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>frukt-/fröspridning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -847,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>671769.7158411201</v>
+        <v>671770</v>
       </c>
       <c r="R3" t="n">
-        <v>6546836.174083618</v>
+        <v>6546836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,24 +869,14 @@
           <t>2006-09-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-09-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>T.a.; Känd tidigare...</t>
+          <t>Känd sedan 1923; Fåtal ex., sent på året !</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +890,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Ädellövskog, mot berg; Rik lövmylla</t>
+          <t>Ädelövskog, mot berg; rik lövmylla</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,15 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>263504</v>
+        <v>96112419</v>
       </c>
       <c r="B4" t="n">
-        <v>97821</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,7 +938,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>273</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,16 +951,18 @@
           <t>i frukt</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ösmo sn, Hammersta, Srm</t>
+          <t>Hammersta gård, ca 400 m ONO om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>671769.7158411201</v>
+        <v>671802</v>
       </c>
       <c r="R4" t="n">
-        <v>6546836.174083618</v>
+        <v>6546722</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,27 +989,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2006-09-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2006-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Känd sedan 1923; Fåtal ex., sent på året !</t>
+          <t>Ganska tätt bestånd, delvis bland nedfallna mindre träd och grenar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,78 +1008,80 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Ädelövskog, mot berg; rik lövmylla</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Rolf Wahlström, Monica Svensson, Stefan Clason</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3784065</v>
+        <v>96113193</v>
       </c>
       <c r="B5" t="n">
-        <v>103345</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221423</v>
+        <v>783</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ösmo sn, Hammersta, Srm</t>
+          <t>Hammersta gård ca 400 m NO om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>671769.7158411201</v>
+        <v>671763</v>
       </c>
       <c r="R5" t="n">
-        <v>6546836.174083618</v>
+        <v>6546765</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1140,27 +1108,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2006-09-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2006-09-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-12</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Lokala grupper</t>
+          <t>En ensam tuva med fem fertila skott. Glesbevuxen lövträdslund med ek och hassel. Delvis bar, lerig jord.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,81 +1127,83 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Ädellövskog, på lera</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Henry Gudmundson</t>
+          <t>Rolf Wahlström, Monica Svensson, Stefan Clason</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>73912763</v>
+        <v>128626838</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>783</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hammersta, Srm</t>
+          <t>Hammersta gård 300 m O om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>671995.2903892467</v>
+        <v>671749</v>
       </c>
       <c r="R6" t="n">
-        <v>6547068.463922672</v>
+        <v>6546642</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1267,22 +1227,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-04-01</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Återfynd. Centralt tämligen tätt bestånd med 748 strån; åt söder 51 strån och i nordväst 55 strån i spridda bestånd. Något färre antal strån än 2021, men fortfarande största beståndet i reservatet</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,73 +1246,80 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karin Kjellberg</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karin Kjellberg</t>
+          <t>Rolf Wahlström, Lisa Lundin, Ulla Sebestyen, Per Johnsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>73925018</v>
+        <v>128627516</v>
       </c>
       <c r="B7" t="n">
-        <v>96312</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100665</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>783</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Skogskorn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Hordelymus europaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Harz</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hammersta, NO om, Srm</t>
+          <t>Hammersta gård, 425 m NO om, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>671957.3110511336</v>
+        <v>671838</v>
       </c>
       <c r="R7" t="n">
-        <v>6546948.200635544</v>
+        <v>6546816</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1384,22 +1346,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2015-08-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2015-08-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Nytt fynd. Litet, samlat bestånd på öppen mark intill stor ek. FV-exkursion.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,27 +1372,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karin Kjellberg</t>
+          <t>Rolf Wahlström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karin Kjellberg</t>
+          <t>Rolf Wahlström, Lisa Lundin, Ulla Sebestyen, Per Johnsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96113193</v>
+        <v>128627592</v>
       </c>
       <c r="B8" t="n">
-        <v>97822</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100666</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1414,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1479,14 +1431,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hammersta gård ca 400 m NO om, Srm</t>
+          <t>Hammersta gård, 465 m NO om, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>671762.5905089076</v>
+        <v>671859</v>
       </c>
       <c r="R8" t="n">
-        <v>6546764.716064104</v>
+        <v>6546851</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1513,27 +1465,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>En ensam tuva med fem fertila skott. Glesbevuxen lövträdslund med ek och hassel. Delvis bar, lerig jord.</t>
+          <t>Ny lokal. Tämligen samlat bestånd i relativt gles skog med hassel och spridda lövträd. FV-exkursion.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1554,17 +1496,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rolf Wahlström, Monica Svensson, Stefan Clason</t>
+          <t>Rolf Wahlström, Lisa Lundin, Ulla Sebestyen, Per Johnsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128627592</v>
+        <v>128628278</v>
       </c>
       <c r="B9" t="n">
-        <v>100193</v>
+        <v>100666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1591,7 +1533,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1599,23 +1541,19 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hammersta gård, 465 m NO om, Srm</t>
+          <t>Hammersta gård, ca 400 m ONO om, nr 3, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>671859</v>
+        <v>671813</v>
       </c>
       <c r="R9" t="n">
-        <v>6546851</v>
+        <v>6546740</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1652,7 +1590,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ny lokal. Tämligen samlat bestånd i relativt gles skog med hassel och spridda lövträd. FV-exkursion.</t>
+          <t>Ny lokal. Två tuvor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,22 +1606,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rolf Wahlström, Lisa Lundin, Ulla Sebestyen, Per Johnsson</t>
+          <t>Monica Svensson, Henry Gudmundson, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128627516</v>
+        <v>128638021</v>
       </c>
       <c r="B10" t="n">
-        <v>100203</v>
+        <v>100665</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,7 +1648,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1727,11 +1665,11 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hammersta gård, 425 m NO om, Srm</t>
+          <t>Hammersta gård, 415 m NO om, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>671838</v>
+        <v>671761</v>
       </c>
       <c r="R10" t="n">
         <v>6546816</v>
@@ -1771,7 +1709,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Nytt fynd. Litet, samlat bestånd på öppen mark intill stor ek. FV-exkursion.</t>
+          <t>Enstaka spridda strån. FV-exkursion.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1799,10 +1737,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128638021</v>
+        <v>128763133</v>
       </c>
       <c r="B11" t="n">
-        <v>100203</v>
+        <v>100665</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,7 +1767,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1846,14 +1784,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hammersta gård, 415 m NO om, Srm</t>
+          <t>Hammersta gård, 495 m NO om, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>671761</v>
+        <v>671857</v>
       </c>
       <c r="R11" t="n">
-        <v>6546816</v>
+        <v>6546886</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1880,17 +1818,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Enstaka spridda strån. FV-exkursion.</t>
+          <t>Samlat bestånd i närheten av stor ek.  Ny lokal, den nordligaste på åkerholmen. Vi genomsöker hela området norr om fram till vägen utan fynd.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1911,68 +1849,57 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rolf Wahlström, Lisa Lundin, Ulla Sebestyen, Per Johnsson</t>
+          <t>Rolf Wahlström, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128763133</v>
+        <v>73925018</v>
       </c>
       <c r="B12" t="n">
-        <v>100212</v>
+        <v>99096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>783</v>
+        <v>219798</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogskorn</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hordelymus europaeus</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Harz</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hammersta gård, 495 m NO om, Srm</t>
+          <t>Hammersta, NO om, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>671857</v>
+        <v>671957</v>
       </c>
       <c r="R12" t="n">
-        <v>6546886</v>
+        <v>6546948</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1999,17 +1926,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2015-08-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Samlat bestånd i närheten av stor ek.  Ny lokal, den nordligaste på åkerholmen. Vi genomsöker hela området norr om fram till vägen utan fynd.</t>
+          <t>2015-08-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2025,15 +1947,547 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rolf Wahlström</t>
+          <t>Karin Kjellberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rolf Wahlström, Ulf Johansson</t>
+          <t>Karin Kjellberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>73925022</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hammersta, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>672003</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6547089</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-08-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-08-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2756399</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110117</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220320</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ängsskära</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Serratula tinctoria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ösmo sn, Hammersta, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>671770</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6546836</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2006-09-12</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2006-09-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>t.a., i omr.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>ädellövskog, ängsmark</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>3784065</v>
+      </c>
+      <c r="B15" t="n">
+        <v>106329</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221423</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Myskmadra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Galium odoratum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ösmo sn, Hammersta, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>671770</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6546836</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2006-09-12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2006-09-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Lokala grupper</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Ädellövskog, på lera</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>73912763</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Hammersta, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>671995</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6547068</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2015-04-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Karin Kjellberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6733858</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102563</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>265350</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vanligt jungfrulin</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ösmo sn, Hammersta, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>671770</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6546836</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nynäshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ösmo</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2006-09-12</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2006-09-12</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>bergsbrant</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henry Gudmundson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27135-2026 artfynd.xlsx
+++ b/artfynd/A 27135-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80064</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/263504</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96112419</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96113193</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128626838</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1381,6 +1411,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627516</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128627592</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1615,6 +1655,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128628278</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1734,6 +1779,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128638021</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1853,6 +1903,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128763133</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1956,6 +2011,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73925018</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2059,6 +2119,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73925022</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2171,6 +2236,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2756399</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2283,6 +2353,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3784065</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2385,6 +2460,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73912763</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2488,8 +2568,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6733858</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>